--- a/artfynd/A 12734-2024 artfynd.xlsx
+++ b/artfynd/A 12734-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120787799</v>
+        <v>120787741</v>
       </c>
       <c r="B2" t="n">
-        <v>57348</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -719,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>448452</v>
+        <v>448437</v>
       </c>
       <c r="R2" t="n">
-        <v>6988269</v>
+        <v>6988459</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -754,7 +749,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,12 +759,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,15 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120787741</v>
+        <v>120787799</v>
       </c>
       <c r="B3" t="n">
-        <v>57348</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -840,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>448437</v>
+        <v>448452</v>
       </c>
       <c r="R3" t="n">
-        <v>6988459</v>
+        <v>6988269</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -875,7 +865,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -885,12 +875,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -914,122 +904,6 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>120787914</v>
-      </c>
-      <c r="B4" t="n">
-        <v>90705</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>Granticka, Jmt</t>
-        </is>
-      </c>
-      <c r="Q4" t="n">
-        <v>448410</v>
-      </c>
-      <c r="R4" t="n">
-        <v>6988377</v>
-      </c>
-      <c r="S4" t="n">
-        <v>1</v>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>Oviken</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>2024-10-31</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>2024-10-31</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
-      <c r="AD4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF4" t="inlineStr"/>
-      <c r="AG4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT4" t="inlineStr"/>
-      <c r="AW4" t="inlineStr">
-        <is>
-          <t>Mona Olsson</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>Mona Olsson</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 12734-2024 artfynd.xlsx
+++ b/artfynd/A 12734-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -788,6 +793,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120787741</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -904,8 +914,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120787799</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>